--- a/cumulative.xlsx
+++ b/cumulative.xlsx
@@ -112,30 +112,10 @@
     <t xml:space="preserve">01.12.2026</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sell rewards if monthly rewards equal 1k+$;
+    <t xml:space="preserve">Sell rewards if monthly rewards equal 700+$;
 Otherwise restake every 2-4 weeks;
 If monthly rewards equal &lt; 330$, increase your stake by buying more coins from market;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">This way your strategy is balanced with income and compounding, thus not losing share of total supply;</t>
-    </r>
+This way your strategy is balanced with income and compounding, thus not losing share of total supply;</t>
   </si>
 </sst>
 </file>
@@ -151,7 +131,7 @@
     <numFmt numFmtId="169" formatCode="#,##0"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,13 +169,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -728,7 +701,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="10" t="n">
-        <v>138000000</v>
+        <v>140000000</v>
       </c>
       <c r="T4" s="6" t="n">
         <v>20</v>
@@ -747,7 +720,7 @@
       </c>
       <c r="X4" s="10" t="n">
         <f aca="false">S4*(1+V4)</f>
-        <v>140112706.928963</v>
+        <v>142143325.869962</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -807,7 +780,7 @@
       </c>
       <c r="S5" s="10" t="n">
         <f aca="false">X4</f>
-        <v>140112706.928963</v>
+        <v>142143325.869962</v>
       </c>
       <c r="T5" s="6" t="n">
         <v>20</v>
@@ -826,7 +799,7 @@
       </c>
       <c r="X5" s="10" t="n">
         <f aca="false">S5*(1+V5)</f>
-        <v>142257758.282329</v>
+        <v>144319464.924102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -886,7 +859,7 @@
       </c>
       <c r="S6" s="10" t="n">
         <f aca="false">X5</f>
-        <v>142257758.282329</v>
+        <v>144319464.924102</v>
       </c>
       <c r="T6" s="6" t="n">
         <v>20</v>
@@ -905,7 +878,7 @@
       </c>
       <c r="X6" s="10" t="n">
         <f aca="false">S6*(1+V6)</f>
-        <v>144435649.236111</v>
+        <v>146528919.514895</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -965,7 +938,7 @@
       </c>
       <c r="S7" s="10" t="n">
         <f aca="false">X6</f>
-        <v>144435649.236111</v>
+        <v>146528919.514895</v>
       </c>
       <c r="T7" s="6" t="n">
         <v>20</v>
@@ -984,7 +957,7 @@
       </c>
       <c r="X7" s="10" t="n">
         <f aca="false">S7*(1+V7)</f>
-        <v>146646882.5472</v>
+        <v>148772199.685566</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1044,7 +1017,7 @@
       </c>
       <c r="S8" s="10" t="n">
         <f aca="false">X7</f>
-        <v>146646882.5472</v>
+        <v>148772199.685566</v>
       </c>
       <c r="T8" s="6" t="n">
         <v>20</v>
@@ -1063,7 +1036,7 @@
       </c>
       <c r="X8" s="10" t="n">
         <f aca="false">S8*(1+V8)</f>
-        <v>148891968.669434</v>
+        <v>151049823.287832</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1123,7 +1096,7 @@
       </c>
       <c r="S9" s="10" t="n">
         <f aca="false">X8</f>
-        <v>148891968.669434</v>
+        <v>151049823.287832</v>
       </c>
       <c r="T9" s="6" t="n">
         <v>20</v>
@@ -1142,7 +1115,7 @@
       </c>
       <c r="X9" s="10" t="n">
         <f aca="false">S9*(1+V9)</f>
-        <v>151171425.871426</v>
+        <v>153362316.101446</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1202,7 +1175,7 @@
       </c>
       <c r="S10" s="10" t="n">
         <f aca="false">X9</f>
-        <v>151171425.871426</v>
+        <v>153362316.101446</v>
       </c>
       <c r="T10" s="6" t="n">
         <v>20</v>
@@ -1221,7 +1194,7 @@
       </c>
       <c r="X10" s="10" t="n">
         <f aca="false">S10*(1+V10)</f>
-        <v>153485780.356207</v>
+        <v>155710211.955572</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1281,7 +1254,7 @@
       </c>
       <c r="S11" s="10" t="n">
         <f aca="false">X10</f>
-        <v>153485780.356207</v>
+        <v>155710211.955572</v>
       </c>
       <c r="T11" s="6" t="n">
         <v>20</v>
@@ -1300,7 +1273,7 @@
       </c>
       <c r="X11" s="10" t="n">
         <f aca="false">S11*(1+V11)</f>
-        <v>155835566.382698</v>
+        <v>158094052.852013</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1360,7 +1333,7 @@
       </c>
       <c r="S12" s="10" t="n">
         <f aca="false">X11</f>
-        <v>155835566.382698</v>
+        <v>158094052.852013</v>
       </c>
       <c r="T12" s="6" t="n">
         <v>20</v>
@@ -1379,7 +1352,7 @@
       </c>
       <c r="X12" s="10" t="n">
         <f aca="false">S12*(1+V12)</f>
-        <v>158221326.389043</v>
+        <v>160514389.090334</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1439,7 +1412,7 @@
       </c>
       <c r="S13" s="10" t="n">
         <f aca="false">X12</f>
-        <v>158221326.389043</v>
+        <v>160514389.090334</v>
       </c>
       <c r="T13" s="6" t="n">
         <v>20</v>
@@ -1458,7 +1431,7 @@
       </c>
       <c r="X13" s="10" t="n">
         <f aca="false">S13*(1+V13)</f>
-        <v>160643611.117825</v>
+        <v>162971779.394894</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1518,7 +1491,7 @@
       </c>
       <c r="S14" s="10" t="n">
         <f aca="false">X13</f>
-        <v>160643611.117825</v>
+        <v>162971779.394894</v>
       </c>
       <c r="T14" s="6" t="n">
         <v>20</v>
@@ -1537,7 +1510,7 @@
       </c>
       <c r="X14" s="10" t="n">
         <f aca="false">S14*(1+V14)</f>
-        <v>163102979.743203</v>
+        <v>165466791.043829</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1597,7 +1570,7 @@
       </c>
       <c r="S15" s="10" t="n">
         <f aca="false">X14</f>
-        <v>163102979.743203</v>
+        <v>165466791.043829</v>
       </c>
       <c r="T15" s="6" t="n">
         <v>20</v>
@@ -1616,7 +1589,7 @@
       </c>
       <c r="X15" s="10" t="n">
         <f aca="false">S15*(1+V15)</f>
-        <v>165600000</v>
+        <v>168000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1676,7 +1649,7 @@
       </c>
       <c r="S16" s="10" t="n">
         <f aca="false">X15</f>
-        <v>165600000</v>
+        <v>168000000</v>
       </c>
       <c r="T16" s="6" t="n">
         <v>20</v>
@@ -1695,7 +1668,7 @@
       </c>
       <c r="X16" s="10" t="n">
         <f aca="false">S16*(1+V16)</f>
-        <v>168135248.314756</v>
+        <v>170571991.043955</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1750,7 +1723,7 @@
       </c>
       <c r="S17" s="10" t="n">
         <f aca="false">X16</f>
-        <v>168135248.314756</v>
+        <v>170571991.043955</v>
       </c>
       <c r="T17" s="6" t="n">
         <v>20</v>
@@ -1769,7 +1742,7 @@
       </c>
       <c r="X17" s="10" t="n">
         <f aca="false">S17*(1+V17)</f>
-        <v>170709309.938795</v>
+        <v>173183357.908923</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1824,7 +1797,7 @@
       </c>
       <c r="S18" s="10" t="n">
         <f aca="false">X17</f>
-        <v>170709309.938795</v>
+        <v>173183357.908923</v>
       </c>
       <c r="T18" s="6" t="n">
         <v>20</v>
@@ -1843,7 +1816,7 @@
       </c>
       <c r="X18" s="10" t="n">
         <f aca="false">S18*(1+V18)</f>
-        <v>173322779.083333</v>
+        <v>175834703.417874</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1898,7 +1871,7 @@
       </c>
       <c r="S19" s="10" t="n">
         <f aca="false">X18</f>
-        <v>173322779.083333</v>
+        <v>175834703.417874</v>
       </c>
       <c r="T19" s="6" t="n">
         <v>20</v>
@@ -1917,7 +1890,7 @@
       </c>
       <c r="X19" s="10" t="n">
         <f aca="false">S19*(1+V19)</f>
-        <v>175976259.05664</v>
+        <v>178526639.622679</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1972,7 +1945,7 @@
       </c>
       <c r="S20" s="10" t="n">
         <f aca="false">X19</f>
-        <v>175976259.05664</v>
+        <v>178526639.622679</v>
       </c>
       <c r="T20" s="6" t="n">
         <v>20</v>
@@ -1991,7 +1964,7 @@
       </c>
       <c r="X20" s="10" t="n">
         <f aca="false">S20*(1+V20)</f>
-        <v>178670362.403321</v>
+        <v>181259787.945398</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2046,7 +2019,7 @@
       </c>
       <c r="S21" s="10" t="n">
         <f aca="false">X20</f>
-        <v>178670362.403321</v>
+        <v>181259787.945398</v>
       </c>
       <c r="T21" s="6" t="n">
         <v>20</v>
@@ -2065,7 +2038,7 @@
       </c>
       <c r="X21" s="10" t="n">
         <f aca="false">S21*(1+V21)</f>
-        <v>181405711.045711</v>
+        <v>184034779.321736</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2120,7 +2093,7 @@
       </c>
       <c r="S22" s="10" t="n">
         <f aca="false">X21</f>
-        <v>181405711.045711</v>
+        <v>184034779.321736</v>
       </c>
       <c r="T22" s="6" t="n">
         <v>20</v>
@@ -2139,7 +2112,7 @@
       </c>
       <c r="X22" s="10" t="n">
         <f aca="false">S22*(1+V22)</f>
-        <v>184182936.427448</v>
+        <v>186852254.346686</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2194,7 +2167,7 @@
       </c>
       <c r="S23" s="10" t="n">
         <f aca="false">X22</f>
-        <v>184182936.427448</v>
+        <v>186852254.346686</v>
       </c>
       <c r="T23" s="6" t="n">
         <v>20</v>
@@ -2213,7 +2186,7 @@
       </c>
       <c r="X23" s="10" t="n">
         <f aca="false">S23*(1+V23)</f>
-        <v>187002679.659238</v>
+        <v>189712863.422415</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2268,7 +2241,7 @@
       </c>
       <c r="S24" s="10" t="n">
         <f aca="false">X23</f>
-        <v>187002679.659238</v>
+        <v>189712863.422415</v>
       </c>
       <c r="T24" s="6" t="n">
         <v>20</v>
@@ -2287,7 +2260,7 @@
       </c>
       <c r="X24" s="10" t="n">
         <f aca="false">S24*(1+V24)</f>
-        <v>189865591.666852</v>
+        <v>192617266.9084</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2322,7 +2295,7 @@
       </c>
       <c r="S25" s="10" t="n">
         <f aca="false">X24</f>
-        <v>189865591.666852</v>
+        <v>192617266.9084</v>
       </c>
       <c r="T25" s="6" t="n">
         <v>20</v>
@@ -2341,7 +2314,7 @@
       </c>
       <c r="X25" s="10" t="n">
         <f aca="false">S25*(1+V25)</f>
-        <v>192772333.341389</v>
+        <v>195566135.273873</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2376,7 +2349,7 @@
       </c>
       <c r="S26" s="10" t="n">
         <f aca="false">X25</f>
-        <v>192772333.341389</v>
+        <v>195566135.273873</v>
       </c>
       <c r="T26" s="6" t="n">
         <v>20</v>
@@ -2395,7 +2368,7 @@
       </c>
       <c r="X26" s="10" t="n">
         <f aca="false">S26*(1+V26)</f>
-        <v>195723575.691844</v>
+        <v>198560149.252595</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2439,7 +2412,7 @@
       </c>
       <c r="S27" s="10" t="n">
         <f aca="false">X26</f>
-        <v>195723575.691844</v>
+        <v>198560149.252595</v>
       </c>
       <c r="T27" s="6" t="n">
         <v>20</v>
@@ -2458,7 +2431,7 @@
       </c>
       <c r="X27" s="10" t="n">
         <f aca="false">S27*(1+V27)</f>
-        <v>198720000</v>
+        <v>201600000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2500,7 +2473,7 @@
       </c>
       <c r="S28" s="10" t="n">
         <f aca="false">X27</f>
-        <v>198720000</v>
+        <v>201600000</v>
       </c>
       <c r="T28" s="6" t="n">
         <v>20</v>
@@ -2519,7 +2492,7 @@
       </c>
       <c r="X28" s="10" t="n">
         <f aca="false">S28*(1+V28)</f>
-        <v>201762297.977707</v>
+        <v>204686389.252746</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2561,7 +2534,7 @@
       </c>
       <c r="S29" s="10" t="n">
         <f aca="false">X28</f>
-        <v>201762297.977707</v>
+        <v>204686389.252746</v>
       </c>
       <c r="T29" s="6" t="n">
         <v>20</v>
@@ -2580,7 +2553,7 @@
       </c>
       <c r="X29" s="10" t="n">
         <f aca="false">S29*(1+V29)</f>
-        <v>204851171.926554</v>
+        <v>207820029.490707</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2622,7 +2595,7 @@
       </c>
       <c r="S30" s="10" t="n">
         <f aca="false">X29</f>
-        <v>204851171.926554</v>
+        <v>207820029.490707</v>
       </c>
       <c r="T30" s="6" t="n">
         <v>20</v>
@@ -2641,7 +2614,7 @@
       </c>
       <c r="X30" s="10" t="n">
         <f aca="false">S30*(1+V30)</f>
-        <v>207987334.899999</v>
+        <v>211001644.101448</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2683,7 +2656,7 @@
       </c>
       <c r="S31" s="10" t="n">
         <f aca="false">X30</f>
-        <v>207987334.899999</v>
+        <v>211001644.101448</v>
       </c>
       <c r="T31" s="6" t="n">
         <v>20</v>
@@ -2702,7 +2675,7 @@
       </c>
       <c r="X31" s="10" t="n">
         <f aca="false">S31*(1+V31)</f>
-        <v>211171510.867968</v>
+        <v>214231967.547214</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2744,7 +2717,7 @@
       </c>
       <c r="S32" s="10" t="n">
         <f aca="false">X31</f>
-        <v>211171510.867968</v>
+        <v>214231967.547214</v>
       </c>
       <c r="T32" s="6" t="n">
         <v>20</v>
@@ -2763,7 +2736,7 @@
       </c>
       <c r="X32" s="10" t="n">
         <f aca="false">S32*(1+V32)</f>
-        <v>214404434.883985</v>
+        <v>217511745.534478</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2805,7 +2778,7 @@
       </c>
       <c r="S33" s="10" t="n">
         <f aca="false">X32</f>
-        <v>214404434.883985</v>
+        <v>217511745.534478</v>
       </c>
       <c r="T33" s="6" t="n">
         <v>20</v>
@@ -2824,7 +2797,7 @@
       </c>
       <c r="X33" s="10" t="n">
         <f aca="false">S33*(1+V33)</f>
-        <v>217686853.254853</v>
+        <v>220841735.186083</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2866,7 +2839,7 @@
       </c>
       <c r="S34" s="10" t="n">
         <f aca="false">X33</f>
-        <v>217686853.254853</v>
+        <v>220841735.186083</v>
       </c>
       <c r="T34" s="6" t="n">
         <v>20</v>
@@ -2885,7 +2858,7 @@
       </c>
       <c r="X34" s="10" t="n">
         <f aca="false">S34*(1+V34)</f>
-        <v>221019523.712938</v>
+        <v>224222705.216024</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2927,7 +2900,7 @@
       </c>
       <c r="S35" s="10" t="n">
         <f aca="false">X34</f>
-        <v>221019523.712938</v>
+        <v>224222705.216024</v>
       </c>
       <c r="T35" s="6" t="n">
         <v>20</v>
@@ -2946,7 +2919,7 @@
       </c>
       <c r="X35" s="10" t="n">
         <f aca="false">S35*(1+V35)</f>
-        <v>224403215.591086</v>
+        <v>227655436.106898</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2981,7 +2954,7 @@
       </c>
       <c r="S36" s="10" t="n">
         <f aca="false">X35</f>
-        <v>224403215.591086</v>
+        <v>227655436.106898</v>
       </c>
       <c r="T36" s="6" t="n">
         <v>20</v>
@@ -3000,7 +2973,7 @@
       </c>
       <c r="X36" s="10" t="n">
         <f aca="false">S36*(1+V36)</f>
-        <v>227838710.000222</v>
+        <v>231140720.29008</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3035,7 +3008,7 @@
       </c>
       <c r="S37" s="10" t="n">
         <f aca="false">X36</f>
-        <v>227838710.000222</v>
+        <v>231140720.29008</v>
       </c>
       <c r="T37" s="6" t="n">
         <v>20</v>
@@ -3054,7 +3027,7 @@
       </c>
       <c r="X37" s="10" t="n">
         <f aca="false">S37*(1+V37)</f>
-        <v>231326800.009667</v>
+        <v>234679362.328648</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3089,7 +3062,7 @@
       </c>
       <c r="S38" s="10" t="n">
         <f aca="false">X37</f>
-        <v>231326800.009667</v>
+        <v>234679362.328648</v>
       </c>
       <c r="T38" s="6" t="n">
         <v>20</v>
@@ -3108,7 +3081,7 @@
       </c>
       <c r="X38" s="10" t="n">
         <f aca="false">S38*(1+V38)</f>
-        <v>234868290.830213</v>
+        <v>238272179.103114</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3143,7 +3116,7 @@
       </c>
       <c r="S39" s="10" t="n">
         <f aca="false">X38</f>
-        <v>234868290.830213</v>
+        <v>238272179.103114</v>
       </c>
       <c r="T39" s="6" t="n">
         <v>20</v>
@@ -3162,7 +3135,7 @@
       </c>
       <c r="X39" s="10" t="n">
         <f aca="false">S39*(1+V39)</f>
-        <v>238464000</v>
+        <v>241920000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3197,7 +3170,7 @@
       </c>
       <c r="S40" s="10" t="n">
         <f aca="false">X39</f>
-        <v>238464000</v>
+        <v>241920000</v>
       </c>
       <c r="T40" s="6" t="n">
         <v>20</v>
@@ -3216,7 +3189,7 @@
       </c>
       <c r="X40" s="10" t="n">
         <f aca="false">S40*(1+V40)</f>
-        <v>242114757.573248</v>
+        <v>245623667.103295</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3251,7 +3224,7 @@
       </c>
       <c r="S41" s="10" t="n">
         <f aca="false">X40</f>
-        <v>242114757.573248</v>
+        <v>245623667.103295</v>
       </c>
       <c r="T41" s="6" t="n">
         <v>20</v>
@@ -3270,7 +3243,7 @@
       </c>
       <c r="X41" s="10" t="n">
         <f aca="false">S41*(1+V41)</f>
-        <v>245821406.311865</v>
+        <v>249384035.388848</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3305,7 +3278,7 @@
       </c>
       <c r="S42" s="10" t="n">
         <f aca="false">X41</f>
-        <v>245821406.311865</v>
+        <v>249384035.388848</v>
       </c>
       <c r="T42" s="6" t="n">
         <v>20</v>
@@ -3324,7 +3297,7 @@
       </c>
       <c r="X42" s="10" t="n">
         <f aca="false">S42*(1+V42)</f>
-        <v>249584801.879999</v>
+        <v>253201972.921738</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3359,7 +3332,7 @@
       </c>
       <c r="S43" s="10" t="n">
         <f aca="false">X42</f>
-        <v>249584801.879999</v>
+        <v>253201972.921738</v>
       </c>
       <c r="T43" s="6" t="n">
         <v>20</v>
@@ -3378,7 +3351,7 @@
       </c>
       <c r="X43" s="10" t="n">
         <f aca="false">S43*(1+V43)</f>
-        <v>253405813.041562</v>
+        <v>257078361.056657</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3413,7 +3386,7 @@
       </c>
       <c r="S44" s="10" t="n">
         <f aca="false">X43</f>
-        <v>253405813.041562</v>
+        <v>257078361.056657</v>
       </c>
       <c r="T44" s="6" t="n">
         <v>20</v>
@@ -3432,7 +3405,7 @@
       </c>
       <c r="X44" s="10" t="n">
         <f aca="false">S44*(1+V44)</f>
-        <v>257285321.860782</v>
+        <v>261014094.641373</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3467,7 +3440,7 @@
       </c>
       <c r="S45" s="10" t="n">
         <f aca="false">X44</f>
-        <v>257285321.860782</v>
+        <v>261014094.641373</v>
       </c>
       <c r="T45" s="6" t="n">
         <v>20</v>
@@ -3486,7 +3459,7 @@
       </c>
       <c r="X45" s="10" t="n">
         <f aca="false">S45*(1+V45)</f>
-        <v>261224223.905824</v>
+        <v>265010082.223299</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3521,7 +3494,7 @@
       </c>
       <c r="S46" s="10" t="n">
         <f aca="false">X45</f>
-        <v>261224223.905824</v>
+        <v>265010082.223299</v>
       </c>
       <c r="T46" s="6" t="n">
         <v>20</v>
@@ -3540,7 +3513,7 @@
       </c>
       <c r="X46" s="10" t="n">
         <f aca="false">S46*(1+V46)</f>
-        <v>265223428.455525</v>
+        <v>269067246.259228</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3575,7 +3548,7 @@
       </c>
       <c r="S47" s="10" t="n">
         <f aca="false">X46</f>
-        <v>265223428.455525</v>
+        <v>269067246.259228</v>
       </c>
       <c r="T47" s="6" t="n">
         <v>20</v>
@@ -3594,7 +3567,7 @@
       </c>
       <c r="X47" s="10" t="n">
         <f aca="false">S47*(1+V47)</f>
-        <v>269283858.709303</v>
+        <v>273186523.328278</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3629,7 +3602,7 @@
       </c>
       <c r="S48" s="10" t="n">
         <f aca="false">X47</f>
-        <v>269283858.709303</v>
+        <v>273186523.328278</v>
       </c>
       <c r="T48" s="6" t="n">
         <v>20</v>
@@ -3648,7 +3621,7 @@
       </c>
       <c r="X48" s="10" t="n">
         <f aca="false">S48*(1+V48)</f>
-        <v>273406452.000267</v>
+        <v>277368864.348096</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3683,7 +3656,7 @@
       </c>
       <c r="S49" s="10" t="n">
         <f aca="false">X48</f>
-        <v>273406452.000267</v>
+        <v>277368864.348096</v>
       </c>
       <c r="T49" s="6" t="n">
         <v>20</v>
@@ -3702,7 +3675,7 @@
       </c>
       <c r="X49" s="10" t="n">
         <f aca="false">S49*(1+V49)</f>
-        <v>277592160.011601</v>
+        <v>281615234.794377</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3737,7 +3710,7 @@
       </c>
       <c r="S50" s="10" t="n">
         <f aca="false">X49</f>
-        <v>277592160.011601</v>
+        <v>281615234.794377</v>
       </c>
       <c r="T50" s="6" t="n">
         <v>20</v>
@@ -3756,7 +3729,7 @@
       </c>
       <c r="X50" s="10" t="n">
         <f aca="false">S50*(1+V50)</f>
-        <v>281841948.996255</v>
+        <v>285926614.923737</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3791,7 +3764,7 @@
       </c>
       <c r="S51" s="10" t="n">
         <f aca="false">X50</f>
-        <v>281841948.996255</v>
+        <v>285926614.923737</v>
       </c>
       <c r="T51" s="6" t="n">
         <v>20</v>
@@ -3810,7 +3783,7 @@
       </c>
       <c r="X51" s="10" t="n">
         <f aca="false">S51*(1+V51)</f>
-        <v>286156800</v>
+        <v>290304000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3845,7 +3818,7 @@
       </c>
       <c r="S52" s="10" t="n">
         <f aca="false">X51</f>
-        <v>286156800</v>
+        <v>290304000</v>
       </c>
       <c r="T52" s="6" t="n">
         <v>20</v>
@@ -3864,7 +3837,7 @@
       </c>
       <c r="X52" s="10" t="n">
         <f aca="false">S52*(1+V52)</f>
-        <v>290537709.087897</v>
+        <v>294748400.523954</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3899,7 +3872,7 @@
       </c>
       <c r="S53" s="10" t="n">
         <f aca="false">X52</f>
-        <v>290537709.087897</v>
+        <v>294748400.523954</v>
       </c>
       <c r="T53" s="6" t="n">
         <v>20</v>
@@ -3918,7 +3891,7 @@
       </c>
       <c r="X53" s="10" t="n">
         <f aca="false">S53*(1+V53)</f>
-        <v>294985687.574238</v>
+        <v>299260842.466618</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3953,7 +3926,7 @@
       </c>
       <c r="S54" s="10" t="n">
         <f aca="false">X53</f>
-        <v>294985687.574238</v>
+        <v>299260842.466618</v>
       </c>
       <c r="T54" s="6" t="n">
         <v>20</v>
@@ -3972,7 +3945,7 @@
       </c>
       <c r="X54" s="10" t="n">
         <f aca="false">S54*(1+V54)</f>
-        <v>299501762.255999</v>
+        <v>303842367.506086</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4007,7 +3980,7 @@
       </c>
       <c r="S55" s="10" t="n">
         <f aca="false">X54</f>
-        <v>299501762.255999</v>
+        <v>303842367.506086</v>
       </c>
       <c r="T55" s="6" t="n">
         <v>20</v>
@@ -4026,7 +3999,7 @@
       </c>
       <c r="X55" s="10" t="n">
         <f aca="false">S55*(1+V55)</f>
-        <v>304086975.649874</v>
+        <v>308494033.267988</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4061,7 +4034,7 @@
       </c>
       <c r="S56" s="10" t="n">
         <f aca="false">X55</f>
-        <v>304086975.649874</v>
+        <v>308494033.267988</v>
       </c>
       <c r="T56" s="6" t="n">
         <v>20</v>
@@ -4080,7 +4053,7 @@
       </c>
       <c r="X56" s="10" t="n">
         <f aca="false">S56*(1+V56)</f>
-        <v>308742386.232939</v>
+        <v>313216913.569648</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4115,7 +4088,7 @@
       </c>
       <c r="S57" s="10" t="n">
         <f aca="false">X56</f>
-        <v>308742386.232939</v>
+        <v>313216913.569648</v>
       </c>
       <c r="T57" s="6" t="n">
         <v>20</v>
@@ -4134,7 +4107,7 @@
       </c>
       <c r="X57" s="10" t="n">
         <f aca="false">S57*(1+V57)</f>
-        <v>313469068.686989</v>
+        <v>318012098.667959</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4169,7 +4142,7 @@
       </c>
       <c r="S58" s="10" t="n">
         <f aca="false">X57</f>
-        <v>313469068.686989</v>
+        <v>318012098.667959</v>
       </c>
       <c r="T58" s="6" t="n">
         <v>20</v>
@@ -4188,7 +4161,7 @@
       </c>
       <c r="X58" s="10" t="n">
         <f aca="false">S58*(1+V58)</f>
-        <v>318268114.14663</v>
+        <v>322880695.511074</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4223,7 +4196,7 @@
       </c>
       <c r="S59" s="10" t="n">
         <f aca="false">X58</f>
-        <v>318268114.14663</v>
+        <v>322880695.511074</v>
       </c>
       <c r="T59" s="6" t="n">
         <v>20</v>
@@ -4242,7 +4215,7 @@
       </c>
       <c r="X59" s="10" t="n">
         <f aca="false">S59*(1+V59)</f>
-        <v>323140630.451163</v>
+        <v>327823827.993933</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4277,7 +4250,7 @@
       </c>
       <c r="S60" s="10" t="n">
         <f aca="false">X59</f>
-        <v>323140630.451163</v>
+        <v>327823827.993933</v>
       </c>
       <c r="T60" s="6" t="n">
         <v>20</v>
@@ -4296,7 +4269,7 @@
       </c>
       <c r="X60" s="10" t="n">
         <f aca="false">S60*(1+V60)</f>
-        <v>328087742.40032</v>
+        <v>332842637.217715</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4331,7 +4304,7 @@
       </c>
       <c r="S61" s="10" t="n">
         <f aca="false">X60</f>
-        <v>328087742.40032</v>
+        <v>332842637.217715</v>
       </c>
       <c r="T61" s="6" t="n">
         <v>20</v>
@@ -4350,7 +4323,7 @@
       </c>
       <c r="X61" s="10" t="n">
         <f aca="false">S61*(1+V61)</f>
-        <v>333110592.013921</v>
+        <v>337938281.753253</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4385,7 +4358,7 @@
       </c>
       <c r="S62" s="10" t="n">
         <f aca="false">X61</f>
-        <v>333110592.013921</v>
+        <v>337938281.753253</v>
       </c>
       <c r="T62" s="6" t="n">
         <v>20</v>
@@ -4404,7 +4377,7 @@
       </c>
       <c r="X62" s="10" t="n">
         <f aca="false">S62*(1+V62)</f>
-        <v>338210338.795506</v>
+        <v>343111937.908484</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4439,7 +4412,7 @@
       </c>
       <c r="S63" s="10" t="n">
         <f aca="false">X62</f>
-        <v>338210338.795506</v>
+        <v>343111937.908484</v>
       </c>
       <c r="T63" s="6" t="n">
         <v>20</v>
@@ -4458,7 +4431,7 @@
       </c>
       <c r="X63" s="10" t="n">
         <f aca="false">S63*(1+V63)</f>
-        <v>343388160</v>
+        <v>348364800</v>
       </c>
     </row>
   </sheetData>
